--- a/datos/workexample.xlsx
+++ b/datos/workexample.xlsx
@@ -344,7 +344,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE24"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="18.88" customWidth="1" style="6" min="1" max="1"/>
@@ -761,298 +761,6 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="M9" s="4" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="M10" s="4" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="M11" s="4" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="M12" s="4" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="M13" s="4" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="M14" s="4" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-    </row>
-    <row r="15">
-      <c r="M15" s="4" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-    </row>
-    <row r="16">
-      <c r="M16" s="4" t="n"/>
-      <c r="N16" s="5" t="n"/>
-      <c r="O16" s="5" t="n"/>
-    </row>
-    <row r="17">
-      <c r="M17" s="4" t="n"/>
-      <c r="N17" s="5" t="n"/>
-      <c r="O17" s="5" t="n"/>
-    </row>
-    <row r="18">
-      <c r="M18" s="4" t="n"/>
-      <c r="N18" s="5" t="n"/>
-      <c r="O18" s="5" t="n"/>
-    </row>
-    <row r="19">
-      <c r="M19" s="4" t="n"/>
-      <c r="N19" s="5" t="n"/>
-      <c r="O19" s="5" t="n"/>
-    </row>
-    <row r="20">
-      <c r="M20" s="4" t="n"/>
-      <c r="N20" s="5" t="n"/>
-      <c r="O20" s="5" t="n"/>
-    </row>
-    <row r="21">
-      <c r="M21" s="4" t="n"/>
-      <c r="N21" s="5" t="n"/>
-      <c r="O21" s="5" t="n"/>
-    </row>
-    <row r="22">
-      <c r="M22" s="4" t="n"/>
-      <c r="N22" s="5" t="n"/>
-      <c r="O22" s="5" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Resonancias del Tiempo</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D23" t="n">
-        <v>8</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Op.12</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Ensemble</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>7</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Fl, Ob, Cl, Vln, Vla, Vc, Pno</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2022-03-15</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Auditorio Nacional</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Madrid</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>Ensemble Intercontemporain</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>Ministerio de Cultura</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Finished</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>For sale</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>SGAE</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>https://youtu.be/example1</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>Obra para conjunto de camara en tres movimientos.</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>Spectralism, Contemporary</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Professional</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Nocturno para Piano</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Version revisada</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>2019</v>
-      </c>
-      <c r="D24" t="n">
-        <v>5</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Op.7</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Solo</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Pno</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Pno</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>2020-01-20</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Sala Gayarre</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Pamplona</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Ana García</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Finished</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Free download</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>SGAE</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>Studio</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Pieza introspectiva en un solo movimiento.</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>Minimalism</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Advanced</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
-    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="R1:V1"/>
